--- a/study_case_model/scenario_variables/demand_scenarios142.xlsx
+++ b/study_case_model/scenario_variables/demand_scenarios142.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21238.61640191083</v>
+        <v>14362.67807379212</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2359.846266878981</v>
+        <v>14362.67807379212</v>
       </c>
     </row>
     <row r="4">
@@ -527,16 +527,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21702.01706294369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -553,11 +553,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>23963.01774121611</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -590,16 +590,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28681.8673061224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -611,12 +611,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -637,11 +637,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7170.4668265306</v>
+        <v>17914.59842145312</v>
       </c>
     </row>
     <row r="11">
@@ -653,16 +653,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52948.32164767363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -674,16 +674,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5971.532807151039</v>
       </c>
     </row>
     <row r="13">
@@ -695,16 +695,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5971.532807151039</v>
       </c>
     </row>
     <row r="14">
@@ -716,7 +716,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16369.41702300738</v>
+        <v>72845.44784612038</v>
       </c>
     </row>
     <row r="15">
@@ -737,7 +737,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -775,20 +775,20 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12472.46748200044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -796,20 +796,20 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1385.829720222271</v>
+        <v>11621.92484478749</v>
       </c>
     </row>
     <row r="19">
@@ -817,16 +817,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -838,20 +838,20 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27002.87699401944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -859,16 +859,16 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -884,16 +884,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="23">
@@ -905,16 +905,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25337.78477374063</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="24">
@@ -926,12 +926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -947,16 +947,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6334.446193435157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -968,7 +968,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51234.25983913136</v>
+        <v>36844.09611630544</v>
       </c>
     </row>
     <row r="27">
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1031,16 +1031,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>16495.55140649507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1052,16 +1052,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>18453.45628118809</v>
       </c>
     </row>
     <row r="31">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1090,20 +1090,20 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19008.30296182249</v>
+        <v>6151.152093729364</v>
       </c>
     </row>
     <row r="33">
@@ -1111,20 +1111,20 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2112.033662424721</v>
+        <v>6151.152093729364</v>
       </c>
     </row>
     <row r="34">
@@ -1132,20 +1132,20 @@
         <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>42957.88421097572</v>
       </c>
     </row>
     <row r="35">
@@ -1153,20 +1153,20 @@
         <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>35570.10580139185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1174,16 +1174,16 @@
         <v>2</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1195,16 +1195,16 @@
         <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1216,11 +1216,11 @@
         <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>33793.38874171551</v>
+        <v>14534.60016344737</v>
       </c>
     </row>
     <row r="39">
@@ -1237,11 +1237,11 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1258,11 +1258,11 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8448.347185428876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1279,20 +1279,20 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>44557.42159340512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1304,16 +1304,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>10762.18365195327</v>
       </c>
     </row>
     <row r="43">
@@ -1325,16 +1325,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>10762.18365195327</v>
       </c>
     </row>
     <row r="44">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10829.36554474711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1388,16 +1388,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>21507.02684822307</v>
       </c>
     </row>
     <row r="47">
@@ -1405,20 +1405,20 @@
         <v>2</v>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>32310.34522054448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1426,20 +1426,20 @@
         <v>2</v>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3590.038357838275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1447,16 +1447,16 @@
         <v>2</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1468,11 +1468,11 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>36846.79109298034</v>
+        <v>16088.83022204715</v>
       </c>
     </row>
     <row r="51">
@@ -1489,11 +1489,11 @@
         <v>2</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1510,11 +1510,11 @@
         <v>2</v>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>5362.943407349052</v>
       </c>
     </row>
     <row r="53">
@@ -1531,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1540,11 +1540,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>16862.83983708039</v>
+        <v>5362.943407349052</v>
       </c>
     </row>
     <row r="54">
@@ -1552,20 +1552,20 @@
         <v>2</v>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>21300.79633013303</v>
       </c>
     </row>
     <row r="55">
@@ -1573,20 +1573,20 @@
         <v>2</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4215.709959270097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>43697.19774356214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1636,20 +1636,20 @@
         <v>2</v>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>6031.558128076127</v>
       </c>
     </row>
     <row r="59">
@@ -1657,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1666,11 +1666,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>11443.3077167731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1699,19 +1699,439 @@
         <v>2</v>
       </c>
       <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" t="n">
         <v>4</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>10391.42176534635</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>10391.42176534635</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>17403.76659749182</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>16414.11299667873</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5471.370998892911</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5471.370998892911</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>36379.63886718184</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2</v>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>7203.861119992658</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>Vår Energi ASA</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
         <v>0</v>
       </c>
     </row>

--- a/study_case_model/scenario_variables/demand_scenarios142.xlsx
+++ b/study_case_model/scenario_variables/demand_scenarios142.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14362.67807379212</v>
+        <v>28725.35614758425</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14362.67807379212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -527,16 +527,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>23963.01774121611</v>
       </c>
     </row>
     <row r="6">
@@ -553,11 +553,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23963.01774121611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -590,16 +590,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>14928.8320178776</v>
       </c>
     </row>
     <row r="9">
@@ -611,12 +611,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -632,16 +632,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17914.59842145312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -658,11 +658,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>29138.17913844815</v>
       </c>
     </row>
     <row r="12">
@@ -679,11 +679,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5971.532807151039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -700,11 +700,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5971.532807151039</v>
+        <v>7284.544784612039</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72845.44784612038</v>
+        <v>46487.69937914996</v>
       </c>
     </row>
     <row r="15">
@@ -779,16 +779,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="18">
@@ -805,11 +805,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11621.92484478749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -838,20 +838,20 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>36844.09611630544</v>
       </c>
     </row>
     <row r="21">
@@ -859,16 +859,16 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -889,11 +889,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11621.98641144057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -905,16 +905,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11621.98641144057</v>
+        <v>30755.76046864681</v>
       </c>
     </row>
     <row r="24">
@@ -926,12 +926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -947,12 +947,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>36844.09611630544</v>
+        <v>10739.47105274393</v>
       </c>
     </row>
     <row r="27">
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1031,16 +1031,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>23255.36026151579</v>
       </c>
     </row>
     <row r="30">
@@ -1057,11 +1057,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18453.45628118809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1078,11 +1078,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>5813.840065378947</v>
       </c>
     </row>
     <row r="32">
@@ -1094,16 +1094,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6151.152093729364</v>
+        <v>43048.73460781306</v>
       </c>
     </row>
     <row r="33">
@@ -1115,16 +1115,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6151.152093729364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1141,11 +1141,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42957.88421097572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1157,16 +1157,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>10753.51342411154</v>
       </c>
     </row>
     <row r="36">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1216,11 +1216,11 @@
         <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14534.60016344737</v>
+        <v>26814.71703674526</v>
       </c>
     </row>
     <row r="39">
@@ -1237,11 +1237,11 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1258,11 +1258,11 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1279,20 +1279,20 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>10650.39816506652</v>
       </c>
     </row>
     <row r="42">
@@ -1304,16 +1304,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>10762.18365195327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1325,16 +1325,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10762.18365195327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>6031.558128076127</v>
       </c>
     </row>
     <row r="45">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1388,16 +1388,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21507.02684822307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1409,16 +1409,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>16626.27482455417</v>
       </c>
     </row>
     <row r="48">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1451,16 +1451,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4156.568706138542</v>
       </c>
     </row>
     <row r="50">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16088.83022204715</v>
+        <v>34807.53319498364</v>
       </c>
     </row>
     <row r="51">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5362.943407349052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1535,16 +1535,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5362.943407349052</v>
+        <v>13678.42749723228</v>
       </c>
     </row>
     <row r="54">
@@ -1556,16 +1556,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21300.79633013303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1594,20 +1594,20 @@
         <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>18189.81943359092</v>
       </c>
     </row>
     <row r="57">
@@ -1615,16 +1615,16 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1636,20 +1636,20 @@
         <v>2</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031.558128076127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1657,20 +1657,20 @@
         <v>2</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>14407.72223998532</v>
       </c>
     </row>
     <row r="60">
@@ -1678,16 +1678,16 @@
         <v>2</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1699,16 +1699,16 @@
         <v>2</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10391.42176534635</v>
+        <v>17996.18288345583</v>
       </c>
     </row>
     <row r="63">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10391.42176534635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1787,16 +1787,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>18645.34219708079</v>
       </c>
     </row>
     <row r="66">
@@ -1808,16 +1808,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>17403.76659749182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1829,16 +1829,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4661.335549270197</v>
       </c>
     </row>
     <row r="68">
@@ -1850,16 +1850,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>51012.92307031886</v>
       </c>
     </row>
     <row r="69">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -1892,16 +1892,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16414.11299667873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1913,16 +1913,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>7157.194301699537</v>
       </c>
     </row>
     <row r="72">
@@ -1934,16 +1934,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5471.370998892911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1955,183 +1955,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5471.370998892911</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>2</v>
-      </c>
-      <c r="B74" t="n">
-        <v>4</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>36379.63886718184</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>2</v>
-      </c>
-      <c r="B75" t="n">
-        <v>4</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>2</v>
-      </c>
-      <c r="B76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>2</v>
-      </c>
-      <c r="B77" t="n">
-        <v>4</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>2</v>
-      </c>
-      <c r="B78" t="n">
-        <v>4</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>7203.861119992658</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2</v>
-      </c>
-      <c r="B79" t="n">
-        <v>4</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" t="n">
-        <v>4</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2</v>
-      </c>
-      <c r="B81" t="n">
-        <v>4</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
         <v>0</v>
       </c>
     </row>
